--- a/dataset_t6_grouped/results2/G4/G4_T1929_W0014F0002T0006Z000C1N30_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1929_W0014F0002T0006Z000C1N30_analysis.xlsx
@@ -480,10 +480,10 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>46.51172326513402</v>
+        <v>7.558155030584278</v>
       </c>
       <c r="D2" t="n">
-        <v>46.86345054621113</v>
+        <v>7.615310713759309</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
